--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118972251</v>
+        <v>118973270</v>
       </c>
       <c r="B2" t="n">
         <v>78228</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479951</v>
+        <v>479903</v>
       </c>
       <c r="R2" t="n">
-        <v>6956579</v>
+        <v>6956786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118972765</v>
+        <v>118972316</v>
       </c>
       <c r="B3" t="n">
         <v>78228</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118971621</v>
+        <v>118973134</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>78228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjeån (Brynjeån), Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480018</v>
+        <v>479876</v>
       </c>
       <c r="R4" t="n">
-        <v>6956565</v>
+        <v>6956682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på mossklädd sten</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118972002</v>
+        <v>118972998</v>
       </c>
       <c r="B5" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479984</v>
+        <v>479916</v>
       </c>
       <c r="R5" t="n">
-        <v>6956533</v>
+        <v>6956691</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118973134</v>
+        <v>118971597</v>
       </c>
       <c r="B6" t="n">
-        <v>78228</v>
+        <v>78136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479876</v>
+        <v>480025</v>
       </c>
       <c r="R6" t="n">
-        <v>6956682</v>
+        <v>6956564</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118972867</v>
+        <v>118972002</v>
       </c>
       <c r="B7" t="n">
-        <v>90661</v>
+        <v>78227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479922</v>
+        <v>479984</v>
       </c>
       <c r="R7" t="n">
-        <v>6956620</v>
+        <v>6956533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1335,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118973508</v>
+        <v>118971564</v>
       </c>
       <c r="B8" t="n">
-        <v>78228</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479958</v>
+        <v>480018</v>
       </c>
       <c r="R8" t="n">
-        <v>6956835</v>
+        <v>6956565</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,22 +1447,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118972948</v>
+        <v>118973016</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>91976</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479912</v>
+        <v>479857</v>
       </c>
       <c r="R9" t="n">
-        <v>6956636</v>
+        <v>6956653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118973270</v>
+        <v>118973237</v>
       </c>
       <c r="B10" t="n">
-        <v>78228</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,34 +1587,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget (Högberget), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479903</v>
+        <v>479887</v>
       </c>
       <c r="R10" t="n">
-        <v>6956786</v>
+        <v>6956782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1661,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,22 +1681,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118971707</v>
+        <v>118971594</v>
       </c>
       <c r="B11" t="n">
-        <v>56502</v>
+        <v>78228</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,43 +1705,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brynjeån (Brynjeån), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480031</v>
+        <v>480018</v>
       </c>
       <c r="R11" t="n">
-        <v>6956543</v>
+        <v>6956565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,22 +1793,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118972216</v>
+        <v>118973118</v>
       </c>
       <c r="B12" t="n">
-        <v>91786</v>
+        <v>78228</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,38 +1817,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget (Högberget), Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479951</v>
+        <v>479847</v>
       </c>
       <c r="R12" t="n">
-        <v>6956579</v>
+        <v>6956705</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,22 +1905,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118973479</v>
+        <v>118971707</v>
       </c>
       <c r="B13" t="n">
-        <v>79600</v>
+        <v>56502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,34 +1933,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åmyren (Åmyren), Jmt</t>
+          <t>Brynjeån (Brynjeån), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479974</v>
+        <v>480031</v>
       </c>
       <c r="R13" t="n">
-        <v>6956814</v>
+        <v>6956543</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118971597</v>
+        <v>118972948</v>
       </c>
       <c r="B14" t="n">
-        <v>78136</v>
+        <v>79600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,38 +2046,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget (Högberget), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480025</v>
+        <v>479912</v>
       </c>
       <c r="R14" t="n">
-        <v>6956564</v>
+        <v>6956636</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,22 +2134,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118971564</v>
+        <v>118972216</v>
       </c>
       <c r="B15" t="n">
-        <v>79572</v>
+        <v>91786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480018</v>
+        <v>479951</v>
       </c>
       <c r="R15" t="n">
-        <v>6956565</v>
+        <v>6956579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118973366</v>
+        <v>118971621</v>
       </c>
       <c r="B16" t="n">
-        <v>78227</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,38 +2270,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Brynjeån (Brynjeån), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479900</v>
+        <v>480018</v>
       </c>
       <c r="R16" t="n">
-        <v>6956794</v>
+        <v>6956565</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2337,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2347,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på mossklädd sten</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,10 +2379,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118973118</v>
+        <v>118973366</v>
       </c>
       <c r="B17" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,21 +2395,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2419,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479847</v>
+        <v>479900</v>
       </c>
       <c r="R17" t="n">
-        <v>6956705</v>
+        <v>6956794</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2464,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,22 +2479,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118973237</v>
+        <v>118973479</v>
       </c>
       <c r="B18" t="n">
-        <v>57290</v>
+        <v>79600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,43 +2503,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Åmyren (Åmyren), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479887</v>
+        <v>479974</v>
       </c>
       <c r="R18" t="n">
-        <v>6956782</v>
+        <v>6956814</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,11 +2577,6 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,7 +2603,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118972998</v>
+        <v>118972251</v>
       </c>
       <c r="B19" t="n">
         <v>78228</v>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479916</v>
+        <v>479951</v>
       </c>
       <c r="R19" t="n">
-        <v>6956691</v>
+        <v>6956579</v>
       </c>
       <c r="S19" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,22 +2703,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118973016</v>
+        <v>118973508</v>
       </c>
       <c r="B20" t="n">
-        <v>91976</v>
+        <v>78228</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,34 +2731,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Brynjeån (Brynjeån), Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479857</v>
+        <v>479958</v>
       </c>
       <c r="R20" t="n">
-        <v>6956653</v>
+        <v>6956835</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,22 +2815,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118972968</v>
+        <v>118972867</v>
       </c>
       <c r="B21" t="n">
-        <v>79572</v>
+        <v>90661</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,38 +2839,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Brynjeån (Brynjeån), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479912</v>
+        <v>479922</v>
       </c>
       <c r="R21" t="n">
-        <v>6956636</v>
+        <v>6956620</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118971594</v>
+        <v>118972968</v>
       </c>
       <c r="B22" t="n">
-        <v>78228</v>
+        <v>79572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,34 +2955,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget (Högberget), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480018</v>
+        <v>479912</v>
       </c>
       <c r="R22" t="n">
-        <v>6956565</v>
+        <v>6956636</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118972998</v>
+        <v>118971597</v>
       </c>
       <c r="B2" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479916</v>
+        <v>480025</v>
       </c>
       <c r="R2" t="n">
-        <v>6956691</v>
+        <v>6956564</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118973016</v>
+        <v>118973679</v>
       </c>
       <c r="B3" t="n">
-        <v>91999</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479857</v>
+        <v>480005</v>
       </c>
       <c r="R3" t="n">
-        <v>6956653</v>
+        <v>6956826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118971621</v>
+        <v>118972867</v>
       </c>
       <c r="B4" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,38 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480018</v>
+        <v>479922</v>
       </c>
       <c r="R4" t="n">
-        <v>6956565</v>
+        <v>6956620</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,19 +969,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på mossklädd sten</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1020,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118973270</v>
+        <v>118973016</v>
       </c>
       <c r="B5" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479903</v>
+        <v>479857</v>
       </c>
       <c r="R5" t="n">
-        <v>6956786</v>
+        <v>6956653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,27 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118972251</v>
+        <v>118972216</v>
       </c>
       <c r="B6" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,27 +1114,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1207,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,50 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118973118</v>
+        <v>118973569</v>
       </c>
       <c r="B7" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479847</v>
+        <v>479987</v>
       </c>
       <c r="R7" t="n">
-        <v>6956705</v>
+        <v>6956884</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118973134</v>
+        <v>118972002</v>
       </c>
       <c r="B8" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,34 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479876</v>
+        <v>479984</v>
       </c>
       <c r="R8" t="n">
-        <v>6956682</v>
+        <v>6956533</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118972867</v>
+        <v>118973366</v>
       </c>
       <c r="B9" t="n">
-        <v>90681</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479922</v>
+        <v>479900</v>
       </c>
       <c r="R9" t="n">
-        <v>6956620</v>
+        <v>6956794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,14 +1504,14 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1580,15 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118972968</v>
+        <v>118971564</v>
       </c>
       <c r="B10" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,14 +1562,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479912</v>
+        <v>480018</v>
       </c>
       <c r="R10" t="n">
-        <v>6956636</v>
+        <v>6956565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118972765</v>
+        <v>118972968</v>
       </c>
       <c r="B11" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,34 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479947</v>
+        <v>479912</v>
       </c>
       <c r="R11" t="n">
-        <v>6956587</v>
+        <v>6956636</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1792,62 +1733,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118971564</v>
+        <v>118972948</v>
       </c>
       <c r="B12" t="n">
-        <v>79592</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480018</v>
+        <v>479912</v>
       </c>
       <c r="R12" t="n">
-        <v>6956565</v>
+        <v>6956636</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,50 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118973508</v>
+        <v>118973479</v>
       </c>
       <c r="B13" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479958</v>
+        <v>479974</v>
       </c>
       <c r="R13" t="n">
-        <v>6956835</v>
+        <v>6956814</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,62 +1947,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118972948</v>
+        <v>118973237</v>
       </c>
       <c r="B14" t="n">
-        <v>79620</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479912</v>
+        <v>479887</v>
       </c>
       <c r="R14" t="n">
-        <v>6956636</v>
+        <v>6956782</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2044,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2128,62 +2064,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118972002</v>
+        <v>118971707</v>
       </c>
       <c r="B15" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479984</v>
+        <v>480031</v>
       </c>
       <c r="R15" t="n">
-        <v>6956533</v>
+        <v>6956543</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2215,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,67 +2176,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monica Magnesved</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118971707</v>
+        <v>118971407</v>
       </c>
       <c r="B16" t="n">
-        <v>56520</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480031</v>
+        <v>480070</v>
       </c>
       <c r="R16" t="n">
-        <v>6956543</v>
+        <v>6956574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2342,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,62 +2283,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118972216</v>
+        <v>118971621</v>
       </c>
       <c r="B17" t="n">
-        <v>91809</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479951</v>
+        <v>480018</v>
       </c>
       <c r="R17" t="n">
-        <v>6956579</v>
+        <v>6956565</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2379,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Växer på mossklädd sten</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,50 +2411,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118973479</v>
+        <v>118971594</v>
       </c>
       <c r="B18" t="n">
-        <v>79620</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åmyren (Åmyren), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479974</v>
+        <v>480018</v>
       </c>
       <c r="R18" t="n">
-        <v>6956814</v>
+        <v>6956565</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2581,27 +2506,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118973237</v>
+        <v>118972251</v>
       </c>
       <c r="B19" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,39 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479887</v>
+        <v>479951</v>
       </c>
       <c r="R19" t="n">
-        <v>6956782</v>
+        <v>6956579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2588,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,12 +2598,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal tall</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,27 +2613,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jan Magnesved</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118971597</v>
+        <v>118972316</v>
       </c>
       <c r="B20" t="n">
-        <v>78156</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,34 +2636,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480025</v>
+        <v>479947</v>
       </c>
       <c r="R20" t="n">
-        <v>6956564</v>
+        <v>6956587</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,15 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118973366</v>
+        <v>118972998</v>
       </c>
       <c r="B21" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2843,37 +2743,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högberget (Högberget), Jmt</t>
+          <t>Brynjeån, Brynjeån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479900</v>
+        <v>479916</v>
       </c>
       <c r="R21" t="n">
-        <v>6956794</v>
+        <v>6956691</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,7 +2802,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2812,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,27 +2827,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Magnesved</t>
+          <t>Monica Magnesved</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118971594</v>
+        <v>118973118</v>
       </c>
       <c r="B22" t="n">
-        <v>78248</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,14 +2870,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brynjeån (Brynjeån), Jmt</t>
+          <t>Högberget, Högberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480018</v>
+        <v>479847</v>
       </c>
       <c r="R22" t="n">
-        <v>6956565</v>
+        <v>6956705</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3014,7 +2909,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3024,7 +2919,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,15 +2934,443 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118973134</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brynjeån, Brynjeån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>479876</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6956682</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118973270</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brynjeån, Brynjeån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>479903</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6956786</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118973508</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brynjeån, Brynjeån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>479958</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6956835</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Monica Magnesved</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118971331</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brynjeån, Brynjeån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>480072</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6956568</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Jan Magnesved</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Jan Magnesved</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973016</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972216</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973569</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972002</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973366</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972968</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972948</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973479</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973237</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971707</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971407</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971621</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971594</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2622,6 +2712,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972251</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972316</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2836,6 +2936,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118972998</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2943,6 +3048,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973118</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3050,6 +3160,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973134</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3157,6 +3272,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973270</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118973508</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3371,8 +3496,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118971331</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91428</v>
+        <v>91567</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91567</v>
+        <v>91569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91571</v>
+        <v>91572</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91572</v>
+        <v>91578</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91578</v>
+        <v>91579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91579</v>
+        <v>91585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91585</v>
+        <v>91592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91593</v>
+        <v>91606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 47986-2022 artfynd.xlsx
+++ b/artfynd/A 47986-2022 artfynd.xlsx
@@ -3395,7 +3395,7 @@
         <v>118971331</v>
       </c>
       <c r="B26" t="n">
-        <v>91606</v>
+        <v>91607</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
